--- a/site/exports/jlu-public-health.xlsx
+++ b/site/exports/jlu-public-health.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,65 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>任淑萍</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>公共卫生学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.jlu.edu.cn/info/1053/3347.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>No independent directory or current personnel check.；No original thesis, degree-conferral record or publisher verification.；教育及论文信息在本留存证据集中为研究员事实摘要，而非完整原文引文；独立复核仅确认摘要与结构化记录一致，未对完整原文逐字核查。仅单位标签和书名保留短引文。 / Education and journal-article information in this retained evidence set consists of researcher factual summaries, not complete verbatim source excerpts. Independent review confirms summary-to-record consistency only, not full original-text verification; only the unit label and book title have short retained quotations.；Own advisors not stated in retained education evidence; empty mentor array means unknown, not absence.；Degree-award events/dates and current employment remain unknown.；来源单位：公共卫生学院／劳动卫生与环境卫生（个人页标签）。本站按“公共卫生学院”归组仅供展示，保留原单位标签；不据此认证法律行政层级、校区或当前任职。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -720,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1783,8 +1837,211 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>任淑萍</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>理学博士学位</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>生物化学与分子生物学</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Education/degree label retained. No explicit conferral verb; endpoint not treated as award date.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.jlu.edu.cn/info/1053/3347.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>任淑萍</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>硕士学位</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>白求恩医科大学</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>卫生毒理学</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Education/degree label retained. No explicit conferral verb; endpoint not treated as award date.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.jlu.edu.cn/info/1053/3347.htm</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>任淑萍</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>医学学士学位</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>白求恩医科大学</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Education/degree label retained. No explicit conferral verb; endpoint not treated as award date.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.jlu.edu.cn/info/1053/3347.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S17"/>
+  <autoFilter ref="A1:S20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1802,6 +2059,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1904,7 +2164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2187,8 +2447,108 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>任淑萍</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.jlu.edu.cn/info/1053/3347.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.jlu.edu.cn/info/1053/3347.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源书目信息（卷）：271；来源书目信息（文章编号）：115939；来源书目信息（doi_as_source）：10.1016/j.ecoenv.2024.115939；来源书目信息（author_token_as_source）：Ren S</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>任淑萍</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>分子生物学检验技术</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.jlu.edu.cn/info/1053/3347.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.jlu.edu.cn/info/1053/3347.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源role_as_source：编者；来源书目信息（date_as_source）：2016年7月</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -2198,6 +2558,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2209,14 +2573,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="60.2" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="57.4" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="44.8" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2406,13 +2770,51 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>任淑萍</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-jlu-renshuping-publichealth-s001-515673747656</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.jlu.edu.cn/info/1053/3347.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:19:30.205765+00:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/jlu-public-health.xlsx
+++ b/site/exports/jlu-public-health.xlsx
@@ -1878,7 +1878,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
